--- a/daily_matches/job_matches_2026-07-07.xlsx
+++ b/daily_matches/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer (Bilingual Mandarin Required)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83640374dcc1134d</t>
+          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (Bilingual Mandarin Required)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Databricks, Power BI, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf10f975373c2da2</t>
+          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Developer-Fullstack</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>CONFIDO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, BigQuery, CI/CD, Snowflake, BigQuery, Kafka, Cassandra, NoSQL, Python</t>
+          <t>Generative AI, RAG, MLflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c41b95cba8e5f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grid Elevated</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TensorFlow, XGBoost, S3, Glue, Athena, Docker, Terraform, Python, SQL, R</t>
+          <t>Data Scientist, RAG, PyTorch, XGBoost, AWS SageMaker, Docker, Kubernetes, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618a1dbe7d6ef58d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc80e7bfc5dd3696</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Data Lake, Dataflow, Terraform, Git, Python, SQL, R</t>
+          <t>Kinesis, FastAPI, CI/CD, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
+          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Technologist - Institutional Operations Technology</t>
+          <t>Agentic AI MCP Integration Specialist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, Kubernetes, CI/CD, Git, Snowflake, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Kubernetes, CI/CD, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
+          <t>https://www.indeed.com/viewjob?jk=879b53b83f9a02ac</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Agentic Engineering Opportunities</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>Relevate Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grovetown, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, PyTorch, MLflow, FastAPI, Docker, Git, Matplotlib, Python, R</t>
+          <t>Copilot, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef753125ece0b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4055d1216d8d7a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer, Clinical Operations</t>
+          <t>Senior Software Engineer — DevOps &amp; Platform, AI Systems</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, MLflow, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Glue, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
+          <t>https://www.indeed.com/viewjob?jk=7dab1f5392ab6e32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c60b208ec927d096</t>
+          <t>https://www.indeed.com/viewjob?jk=f74a8f7842f7ee88</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solution Architect - Enterprise Systems</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ritchie Bros.</t>
+          <t>Zagg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b305d3debd8b67a2</t>
+          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Business Analyst - ELN and LIMS</t>
+          <t>Senior Development Operations Engineer (ScriptingAutomation)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Sunbird Software Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b0c380ec415a81</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2f3fdbd6057ba0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technical Product Owner - Snowflake</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associated Bank</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Snowflake, Kafka, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Docker, Terraform, Snowflake, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
+          <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, R, Java, Scala</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f713ec954690e442</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - AI/ML</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Schweitzer Engineering Laboratories</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pullman, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Docker, Git, PostgreSQL, MongoDB, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Docker, Terraform, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc8d99b3d35b4c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f52ad256fe7a32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer I - AI</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chamberlain Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, S3, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,357 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f913d446752eea</t>
+          <t>https://www.indeed.com/viewjob?jk=559e16a997833e33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Autonomy Services)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1819cf76c3c94e26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer (Autonomy Services)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80bd8e99eaa8aa87</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Santa Barbara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Red Team Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>White Circle</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Copilot, Mistral, AKS, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd11b6512e2fcb15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist Associate</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f139284387823c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=843ae7bb7895613c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c214360962f6b26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Cloud Microservices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Anderson Merchandisers</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acb9e380501578b5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-07.xlsx
+++ b/daily_matches/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior AI Engineer, Legal - USA Remote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Danaher</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf8a59a6869ac6a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Databricks, Power BI, Python</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
+          <t>https://www.indeed.com/viewjob?jk=22caac5643ade2f5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CONFIDO</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, MLflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka</t>
+          <t>RAG, Data Lake, CI/CD, Git, Databricks, Kafka, Hadoop, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
+          <t>https://www.indeed.com/viewjob?jk=f98bbbcdc847f11c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Software Engineer – Agentic AI System</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, XGBoost, AWS SageMaker, Docker, Kubernetes, Git, Snowflake, Databricks</t>
+          <t>LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc80e7bfc5dd3696</t>
+          <t>https://www.indeed.com/viewjob?jk=6560d5cb80e2c5c4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kinesis, FastAPI, CI/CD, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Data Lake, Dataflow, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,312 +636,312 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
+          <t>https://www.indeed.com/viewjob?jk=8965662ac1318ff5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agentic AI MCP Integration Specialist</t>
+          <t>Mechanical Design Integrations Backend Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Kubernetes, CI/CD, Snowflake, Databricks, Python</t>
+          <t>Copilot, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879b53b83f9a02ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f5048a7e029a51a6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agentic Engineering Opportunities</t>
+          <t>Mechanical Design Integrations Backend Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Relevate Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java, Scala</t>
+          <t>Copilot, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4055d1216d8d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=da80569d1b85400b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — DevOps &amp; Platform, AI Systems</t>
+          <t>CAD Integrations Backend Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Glue, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>Copilot, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dab1f5392ab6e32</t>
+          <t>https://www.indeed.com/viewjob?jk=26c8b6e164f8e13d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>CAD Integrations Backend Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+          <t>Copilot, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f74a8f7842f7ee88</t>
+          <t>https://www.indeed.com/viewjob?jk=b02c9ed71db4f4cc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solution Architect - Enterprise Systems</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zagg</t>
+          <t>ABHITO LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7ea523c272d79a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Development Operations Engineer (ScriptingAutomation)</t>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sunbird Software Inc.</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2f3fdbd6057ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=435ad1bbdf233be6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Terraform, Snowflake, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
+          <t>https://www.indeed.com/viewjob?jk=4f535577a3e0e4ab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, MongoDB, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a509da11b6d2e81a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Hibu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Terraform, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, S3, CI/CD, Git, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f52ad256fe7a32</t>
+          <t>https://www.indeed.com/viewjob?jk=eefaed1149d3c0ce</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hibu</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, S3, Python, R, Scala</t>
+          <t>RAG, Prompt Engineering, S3, CI/CD, Git, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559e16a997833e33</t>
+          <t>https://www.indeed.com/viewjob?jk=00566a4ebdd31c4e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Autonomy Services)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Hibu</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, S3, CI/CD, Git, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1819cf76c3c94e26</t>
+          <t>https://www.indeed.com/viewjob?jk=c9b3b06723182d1d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer (Autonomy Services)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bd8e99eaa8aa87</t>
+          <t>https://www.indeed.com/viewjob?jk=f995d68fe8faae3c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>AI ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R</t>
+          <t>Generative AI, Copilot, Git, Databricks, Kafka, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2b763e5ef2d69a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+          <t>https://www.indeed.com/viewjob?jk=8386661830d59ed7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff019b977348ee2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Red Team Engineer</t>
+          <t>Senior Research Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>White Circle</t>
+          <t>Pros.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Mistral, AKS, Python, R, Optimization</t>
+          <t>RAG, Prompt Engineering, TensorFlow, Git, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd11b6512e2fcb15</t>
+          <t>https://www.indeed.com/viewjob?jk=8052f4b3725b9f92</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist Associate</t>
+          <t>Data Scientist Senior</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Snowflake, NoSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,112 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f139284387823c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Scientist</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=843ae7bb7895613c</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c214360962f6b26</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Cloud Microservices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Anderson Merchandisers</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acb9e380501578b5</t>
+          <t>https://www.indeed.com/viewjob?jk=10c0436bfb4c5787</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-07.xlsx
+++ b/daily_matches/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, Legal - USA Remote</t>
+          <t>Applied AI Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf8a59a6869ac6a</t>
+          <t>https://www.indeed.com/viewjob?jk=811f44afc6947919</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Applied AI Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22caac5643ade2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=276f41ff04ea979b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Senior AI Platform Engineer - Frisco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Databricks, Kafka, Hadoop, NoSQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98bbbcdc847f11c</t>
+          <t>https://www.indeed.com/viewjob?jk=82102bbab69e4375</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer – Agentic AI System</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Symmons Industries</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+          <t>Docker, AKS, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,637 +601,217 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6560d5cb80e2c5c4</t>
+          <t>https://www.indeed.com/viewjob?jk=4a21efb839f07ae1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Backend Engineer (Golang) – Trading Systems</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ostium Labs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Data Lake, Dataflow, Terraform, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Git, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8965662ac1318ff5</t>
+          <t>https://www.indeed.com/viewjob?jk=e90a72fcbd4fd175</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mechanical Design Integrations Backend Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5048a7e029a51a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b6cffd2c18251400</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mechanical Design Integrations Backend Engineer</t>
+          <t>Sr Engineer, AI Implementation - remote opportunity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tivity Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da80569d1b85400b</t>
+          <t>https://www.indeed.com/viewjob?jk=c99ba93e4c332c0f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAD Integrations Backend Engineer</t>
+          <t>AI Engineer (Computer Vision/Signal Processing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c8b6e164f8e13d</t>
+          <t>https://www.indeed.com/viewjob?jk=c02327091b3cf469</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAD Integrations Backend Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02c9ed71db4f4cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4acb2c53d4b717</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ABHITO LLC</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7ea523c272d79a</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Logic, Inc.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=435ad1bbdf233be6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Subway</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Shelton, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f535577a3e0e4ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Subway</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Shelton, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a509da11b6d2e81a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Hibu</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, S3, CI/CD, Git, MongoDB, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eefaed1149d3c0ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Hibu</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Cedar Rapids, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, S3, CI/CD, Git, MongoDB, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00566a4ebdd31c4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Hibu</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>King of Prussia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, S3, CI/CD, Git, MongoDB, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9b3b06723182d1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Corpay</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f995d68fe8faae3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Franklin, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, Copilot, Git, Databricks, Kafka, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2b763e5ef2d69a</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Test Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Southfield, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8386661830d59ed7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>I8IS INC.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff019b977348ee2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Research Scientist</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Pros.</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, TensorFlow, Git, Databricks, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8052f4b3725b9f92</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Scientist Senior</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>USAA</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Snowflake, NoSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10c0436bfb4c5787</t>
+          <t>https://www.indeed.com/viewjob?jk=c75c71cc85710139</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-07.xlsx
+++ b/daily_matches/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,157 +468,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Applied AI Product Engineer (Remote Opportunity)</t>
+          <t>Senior Software Data Architect (Phoenix)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Data Lake, CI/CD, Databricks, PySpark, PostgreSQL, MongoDB, Cassandra, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811f44afc6947919</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f3ddd34aabe8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Applied AI Product Engineer (Remote Opportunity)</t>
+          <t>Associate IE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>MasonHub</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fontana, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276f41ff04ea979b</t>
+          <t>https://www.indeed.com/viewjob?jk=917a5a33eee2bc01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer - Frisco</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Kubernetes, CI/CD, Terraform</t>
+          <t>Generative AI, RAG, Cortex, Data Lake, Snowflake, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82102bbab69e4375</t>
+          <t>https://www.indeed.com/viewjob?jk=748c7729e8f9ad32</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Scientist – Decision Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Symmons Industries</t>
+          <t>Scalable Systems Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Docker, AKS, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Tableau, Power BI, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a21efb839f07ae1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb8daae5292d0d9e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Engineer (Golang) – Trading Systems</t>
+          <t>Senior Data Scientist – Decision Analytics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ostium Labs</t>
+          <t>Scalable Systems Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Tableau, Power BI, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,182 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90a72fcbd4fd175</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cushman &amp; Wakefield</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6cffd2c18251400</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sr Engineer, AI Implementation - remote opportunity</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Tivity Health</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c99ba93e4c332c0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI Engineer (Computer Vision/Signal Processing</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Milpitas, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c02327091b3cf469</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Cushman &amp; Wakefield</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4acb2c53d4b717</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c75c71cc85710139</t>
+          <t>https://www.indeed.com/viewjob?jk=2799e537695c862b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-07.xlsx
+++ b/daily_matches/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect (Phoenix)</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, PySpark, PostgreSQL, MongoDB, Cassandra, NoSQL, Power BI</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Redshift, BigQuery, Synapse</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f3ddd34aabe8</t>
+          <t>https://www.indeed.com/viewjob?jk=2f059896b1dc8546</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate IE</t>
+          <t>Agentic AI Engineer (AWS &amp; Azure)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MasonHub</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fontana, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, S3, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917a5a33eee2bc01</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc8098824f5428a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer IV (6226)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, Data Lake, Snowflake, Kafka, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748c7729e8f9ad32</t>
+          <t>https://www.indeed.com/viewjob?jk=966a231d0ac3ac5d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Decision Analytics</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scalable Systems Inc</t>
+          <t>Forman Technology Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Tableau, Power BI, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Git, PostgreSQL, MySQL, NoSQL, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,1897 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb8daae5292d0d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=b706dbf028db0cd8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Decision Analytics</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Scalable Systems Inc</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Glue, Athena, Kinesis, Docker, Kubernetes, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3bbc064985e6d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior AI Infrastructure Engineer, LLM/AI Platforms</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, PyTorch, MLflow, Docker, Kubernetes, Terraform, Dask</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3629f388c5998ab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>doctronic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50e9733baab869ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HAVI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14e0af7fcb6718f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HAVI Logistics GmbH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f7eb8898b893b80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Edwards Lifesciences</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a0870a3d36d95fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Co-Op Data Science/Analytics</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CSL Plasma</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Tableau, Power BI, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04d905bcd26c07f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack )</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f83d3084bf63664</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack )</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adca8b7879a5e5f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack )</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c6153092518a5fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack )</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57cbe54e432ca38f</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0bce03fff5003c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75f0a9682b6674f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbf123e0d6ad9551</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=251c215782320243</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc7a1f895b87013c</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31cc642a695ccc8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc77c78030f02f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=065011cf2412475c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4efc786d22d73d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4f5c73667cedcba</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0045ab67a14cd28e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b800e848a31dbd91</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00d68909b19af093</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b441d1d78f18c32e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6b71a130f4b9a93</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76f9ed627bcd2f2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d7f4cce44cd9f58</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db099dac59f8fc45</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78bd19a2ac73e0e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72c132aa3cb13db5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98525210f71c8b57</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27d9aad043d130bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d087444bcce657e</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62bb5ce2248e0dda</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bb3112cc4da90e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93bf46810918339c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbe470d589707735</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74cbb310805d6aac</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c48e86df906c9af</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48e598f5e36f4058</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a08401fa6113ecb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1efad7a3a73d74f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3daf0ba8555c7dd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70af80dd4de2c2f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Culver City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5c236a3031412b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22cca2fedac886c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Healthcare Payer AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd886dbdf1fe3670</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Cloud Security - FCS Registration (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, Tableau, Power BI, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2799e537695c862b</t>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Kafka, PostgreSQL, Cassandra, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e288afbe233b4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GRP Solutions</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8af4bf4156cd21c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Rhombus Power</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=373957dcbb4e4adb</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Automation Enablement Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Conagra Brands</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdbf7cdb882c5ba2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Conagra Brands</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Redshift, Data Lake, Snowflake, Databricks, Redshift, PySpark, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52047d4398660a13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI Development Specialist - Claude,CHATGPT</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Streamline Advance</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b58646cec1775e3c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-07.xlsx
+++ b/daily_matches/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Sr Data Engineer BI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Quality Bicycle Products GBC / QBP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Redshift, BigQuery, Synapse</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f059896b1dc8546</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcb545e0d7339df</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer (AWS &amp; Azure)</t>
+          <t>DevOps Engineer II - Data and Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, S3, FastAPI, Docker</t>
+          <t>RAG, S3, CI/CD, Terraform, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc8098824f5428a</t>
+          <t>https://www.indeed.com/viewjob?jk=53108c9bd68716fa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer IV (6226)</t>
+          <t>DevOps Engineer II - Data and Analytics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery</t>
+          <t>RAG, S3, CI/CD, Terraform, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966a231d0ac3ac5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2217093bc52c879</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Forman Technology Group</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Git, PostgreSQL, MySQL, NoSQL, Tableau, Power BI</t>
+          <t>RAG, Gemini, Copilot, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b706dbf028db0cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=850828fdab44abc4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Athena, Kinesis, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>RAG, S3, Athena, CI/CD, Terraform, Git, Snowflake, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bbc064985e6d03</t>
+          <t>https://www.indeed.com/viewjob?jk=859a8b68a930992d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer, LLM/AI Platforms</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, PyTorch, MLflow, Docker, Kubernetes, Terraform, Dask</t>
+          <t>RAG, S3, Athena, CI/CD, Terraform, Git, Snowflake, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3629f388c5998ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d34fc4ec0585703</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, S3, Athena, CI/CD, Terraform, Git, Snowflake, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e9733baab869ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccc4b2641f8512d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, DevOps - Austin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HAVI</t>
+          <t>CS Disco</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, SQL, R</t>
+          <t>S3, EC2, Redshift, Kinesis, Docker, CI/CD, Jenkins, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e0af7fcb6718f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4fabdb31d720bc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HAVI Logistics GmbH</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7eb8898b893b80</t>
+          <t>https://www.indeed.com/viewjob?jk=bc73a795e20ebb26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0870a3d36d95fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f293050f94f852b1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Co-Op Data Science/Analytics</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CSL Plasma</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Tableau, Power BI, Python, SQL, R, Hypothesis Testing</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d905bcd26c07f0</t>
+          <t>https://www.indeed.com/viewjob?jk=b685af16a4e1a32c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack )</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f83d3084bf63664</t>
+          <t>https://www.indeed.com/viewjob?jk=401ff47825aadd13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack )</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adca8b7879a5e5f3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb43d49de8a46b2a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack )</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6153092518a5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fb77a8047e2cb8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack )</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57cbe54e432ca38f</t>
+          <t>https://www.indeed.com/viewjob?jk=72319d23cc87f97d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0bce03fff5003c9</t>
+          <t>https://www.indeed.com/viewjob?jk=bad85604b0a1225d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f0a9682b6674f1</t>
+          <t>https://www.indeed.com/viewjob?jk=af5d8aeb243630fb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf123e0d6ad9551</t>
+          <t>https://www.indeed.com/viewjob?jk=fad39d3239661981</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251c215782320243</t>
+          <t>https://www.indeed.com/viewjob?jk=6cbd10dae618111f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7a1f895b87013c</t>
+          <t>https://www.indeed.com/viewjob?jk=92694dec4db4a1f7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Gemini, Copilot, Synapse, Git, PySpark, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cc642a695ccc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=721e7b4ba50acdd1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Associate Business Systems Analyst, Tax &amp; Accountingt</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc77c78030f02f7</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd7e94d87371a7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Sr. Data Analyst - Optum Financial - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=065011cf2412475c</t>
+          <t>https://www.indeed.com/viewjob?jk=055e971d3283b277</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>MongoDB Database Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Viridien</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4efc786d22d73d6</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb0b7ebb1731963</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>DevOps Engineer II - Applications</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f5c73667cedcba</t>
+          <t>https://www.indeed.com/viewjob?jk=59aa31ae2455aa90</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>DevOps Engineer II - Applications</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0045ab67a14cd28e</t>
+          <t>https://www.indeed.com/viewjob?jk=b08b3cca13d3f057</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Software Engineer III - Backend-Focused Full Stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Alliance Technical Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b800e848a31dbd91</t>
+          <t>https://www.indeed.com/viewjob?jk=6da12d7bcb1dbe77</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>(USA) Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, CI/CD, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d68909b19af093</t>
+          <t>https://www.indeed.com/viewjob?jk=367111c50f095519</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Senior Analyst, Data Science</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b441d1d78f18c32e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9181b53e7411ece</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Sr. Full-Stack Developer - AI-forward</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b71a130f4b9a93</t>
+          <t>https://www.indeed.com/viewjob?jk=68312e7121f4a030</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76f9ed627bcd2f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=7be08795791a3dc9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, FastAPI, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,917 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7f4cce44cd9f58</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db099dac59f8fc45</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78bd19a2ac73e0e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72c132aa3cb13db5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98525210f71c8b57</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27d9aad043d130bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d087444bcce657e</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62bb5ce2248e0dda</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb3112cc4da90e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93bf46810918339c</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Walnut Creek, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe470d589707735</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74cbb310805d6aac</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c48e86df906c9af</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48e598f5e36f4058</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a08401fa6113ecb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1efad7a3a73d74f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3daf0ba8555c7dd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70af80dd4de2c2f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Culver City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c236a3031412b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22cca2fedac886c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Healthcare Payer AI Decision Science Consultant</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd886dbdf1fe3670</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Cloud Security - FCS Registration (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Kafka, PostgreSQL, Cassandra, SQL, R</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e288afbe233b4df</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>GRP Solutions</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Texas City, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8af4bf4156cd21c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Rhombus Power</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, MySQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=373957dcbb4e4adb</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior Automation Enablement Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Conagra Brands</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, CI/CD, Terraform, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbf7cdb882c5ba2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Conagra Brands</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Redshift, Data Lake, Snowflake, Databricks, Redshift, PySpark, Power BI, SQL, R</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52047d4398660a13</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AI Development Specialist - Claude,CHATGPT</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Streamline Advance</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Jericho, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Generative AI, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b58646cec1775e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=19211b18854253ce</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-07.xlsx
+++ b/daily_matches/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer BI</t>
+          <t>Senior Specialty AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quality Bicycle Products GBC / QBP</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Snowflake, Databricks, PySpark</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcb545e0d7339df</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc24cce54c5e205</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - Data and Analytics</t>
+          <t>Senior Applied Machine Learning Engineer, Asset Intelligence</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MaintainX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Terraform, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, MLflow, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53108c9bd68716fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d974ea4ce0874c45</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - Data and Analytics</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sorenson Communications</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Terraform, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2217093bc52c879</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab41305de4a58ac</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL</t>
+          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850828fdab44abc4</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7891b7fbaff3f7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, CI/CD, Terraform, Git, Snowflake, PostgreSQL, MySQL, SQL</t>
+          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859a8b68a930992d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a787addd6be5560</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>AI/ML Engineer-ICL-Open Rank (Entry-Junior Level)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, CI/CD, Terraform, Git, Snowflake, PostgreSQL, MySQL, SQL</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d34fc4ec0585703</t>
+          <t>https://www.indeed.com/viewjob?jk=758c22b01275b7e7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, CI/CD, Terraform, Git, Snowflake, PostgreSQL, MySQL, SQL</t>
+          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccc4b2641f8512d</t>
+          <t>https://www.indeed.com/viewjob?jk=86bb84788078c2e2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer, DevOps - Austin</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CS Disco</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, EC2, Redshift, Kinesis, Docker, CI/CD, Jenkins, Terraform, Git, Redshift</t>
+          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4fabdb31d720bc</t>
+          <t>https://www.indeed.com/viewjob?jk=92af747fddea0145</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc73a795e20ebb26</t>
+          <t>https://www.indeed.com/viewjob?jk=af65f1b505eed8e6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>GIS Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Terraform, Git, Snowflake, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f293050f94f852b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8c2320056095b2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b685af16a4e1a32c</t>
+          <t>https://www.indeed.com/viewjob?jk=18521f120cecfb99</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401ff47825aadd13</t>
+          <t>https://www.indeed.com/viewjob?jk=752b32922bfcc8c2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb43d49de8a46b2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cbdf8c3d5d2aa6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Backend Developer, Specialist- C#/ .Net</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Kafka, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fb77a8047e2cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=30a6cad0b5e84df8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Business Systems Analyst - Semantic Layer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>RAG, Synapse, AKS, CI/CD, Git, Snowflake, Databricks, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72319d23cc87f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3ffb67df20da06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Scientist – Demand Forecasting</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad85604b0a1225d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbd0bba4b9b97da0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Advanced Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsford, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, Matplotlib, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5d8aeb243630fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2926491651001d49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad39d3239661981</t>
+          <t>https://www.indeed.com/viewjob?jk=8bacfdd04e1ff4b8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cbd10dae618111f</t>
+          <t>https://www.indeed.com/viewjob?jk=17e015eb77723b36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92694dec4db4a1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=27bbd0b4918a6d96</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Synapse, Git, PySpark, Python, SQL, R, Optimization</t>
+          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721e7b4ba50acdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5a7ee67548d64c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate Business Systems Analyst, Tax &amp; Accountingt</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd7e94d87371a7</t>
+          <t>https://www.indeed.com/viewjob?jk=53812862ed0afc59</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Optum Financial - Remote</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Howard Hughes Medical Institute</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, AKS, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055e971d3283b277</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c634966e3d881c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MongoDB Database Engineer</t>
+          <t>Cost Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Viridien</t>
+          <t>Zelis Healthcare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
+          <t>RAG, Kafka, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,287 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb0b7ebb1731963</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DevOps Engineer II - Applications</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59aa31ae2455aa90</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DevOps Engineer II - Applications</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b08b3cca13d3f057</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Backend-Focused Full Stack</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Alliance Technical Group</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6da12d7bcb1dbe77</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>(USA) Senior, Software Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Sam's Club</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, CI/CD, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=367111c50f095519</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Data Science</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>LPL Financial</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9181b53e7411ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Sr. Full-Stack Developer - AI-forward</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Smarsh</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68312e7121f4a030</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Litera</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Git, PostgreSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7be08795791a3dc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Bristol Myers Squibb</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, FastAPI, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19211b18854253ce</t>
+          <t>https://www.indeed.com/viewjob?jk=078e1151a7e26811</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-07.xlsx
+++ b/daily_matches/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Specialty AI Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, Glue, BigQuery, Kinesis, Dataflow, Kubernetes, Apache Airflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc24cce54c5e205</t>
+          <t>https://www.indeed.com/viewjob?jk=5db19e3a9cbf828d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Applied Machine Learning Engineer, Asset Intelligence</t>
+          <t>Senior DevOps Engineer, GCPay</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MaintainX</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, MLflow, Docker</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d974ea4ce0874c45</t>
+          <t>https://www.indeed.com/viewjob?jk=03e18e9b5df80b70</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Research AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sorenson Communications</t>
+          <t>University of Arizona</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Azure ML, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab41305de4a58ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2455664260de809b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7891b7fbaff3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=6f47ececd784791d</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a787addd6be5560</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3824264dc26ac6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Engineer-ICL-Open Rank (Entry-Junior Level)</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Python</t>
+          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c22b01275b7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2265ad8dcef15915</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>LangChain, RAG, Docker, Kubernetes, Jenkins, Git, Kafka, MySQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86bb84788078c2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d54c186e0fe4fd8f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior Developer – Connected Customer (Loyalty Platform)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Kubernetes, Jenkins, Git, Kafka, Hadoop, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92af747fddea0145</t>
+          <t>https://www.indeed.com/viewjob?jk=764638c30ee52f22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Software Engineer II-Python/PySpark</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af65f1b505eed8e6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c18066ab7c80217</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GIS Software Engineer</t>
+          <t>Business Systems Analyst - Semantic Layer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Terraform, Git, Snowflake, PostgreSQL, Python, SQL</t>
+          <t>RAG, Synapse, AKS, CI/CD, Git, Snowflake, Databricks, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8c2320056095b2</t>
+          <t>https://www.indeed.com/viewjob?jk=97283fc0220405a0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18521f120cecfb99</t>
+          <t>https://www.indeed.com/viewjob?jk=a643cac03a3c91ab</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Senior Software Engineer, C&amp;I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, Python</t>
+          <t>S3, CI/CD, Snowflake, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b32922bfcc8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a602fd90cf822f8c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Software Engineer, C&amp;I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
+          <t>S3, CI/CD, Snowflake, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cbdf8c3d5d2aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=095f422ac934ee58</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Backend Developer, Specialist- C#/ .Net</t>
+          <t>Senior Software Engineer, C&amp;I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Kafka, NoSQL, SQL, R, Java</t>
+          <t>S3, CI/CD, Snowflake, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a6cad0b5e84df8</t>
+          <t>https://www.indeed.com/viewjob?jk=deaff1cd6031383e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Business Systems Analyst - Semantic Layer</t>
+          <t>Senior Software Engineer, C&amp;I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Synapse, AKS, CI/CD, Git, Snowflake, Databricks, NoSQL, SQL, R</t>
+          <t>S3, CI/CD, Snowflake, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3ffb67df20da06</t>
+          <t>https://www.indeed.com/viewjob?jk=253a1410e2b36c94</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist – Demand Forecasting</t>
+          <t>Senior Software Engineer, C&amp;I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>S3, CI/CD, Snowflake, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbd0bba4b9b97da0</t>
+          <t>https://www.indeed.com/viewjob?jk=33fd0b602811c81f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Advanced Data Scientist</t>
+          <t>Sr. Software Engineer (Data Science/Data Engineering)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsford, NY, US USA</t>
+          <t>Bastrop, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, Matplotlib, Python, SQL, R, Java</t>
+          <t>PyTorch, OpenCV, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,252 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2926491651001d49</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bacfdd04e1ff4b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17e015eb77723b36</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27bbd0b4918a6d96</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5a7ee67548d64c</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53812862ed0afc59</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Howard Hughes Medical Institute</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, AKS, CI/CD, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c634966e3d881c</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Cost Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Zelis Healthcare</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Kafka, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=078e1151a7e26811</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d50e54bedc7b3c</t>
         </is>
       </c>
     </row>
